--- a/outputs/EVINV-POC-001/phase3/phase3-early-dfm-findings-register.xlsx
+++ b/outputs/EVINV-POC-001/phase3/phase3-early-dfm-findings-register.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 3 | Gate: 3 | Generated: 2026-08-18T13:22:49.735Z</v>
+        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 3 | Gate: 3 | Generated: 2026-08-18T20:03:14.154Z</v>
       </c>
     </row>
     <row r="4">
